--- a/artfynd/S 171-2026 artfynd.xlsx
+++ b/artfynd/S 171-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733255</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733233</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733254</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733217</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733225</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733264</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733258</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733215</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733220</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733222</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733226</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733228</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733240</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733263</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733267</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2330,6 +2415,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733272</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733214</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2524,6 +2619,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733218</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733234</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733261</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2823,6 +2933,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733236</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2924,6 +3039,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733260</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3021,6 +3141,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733270</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3118,6 +3243,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733266</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3215,8 +3345,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119733221</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>